--- a/EDGAR_Form4_Insider_Purchases.xlsx
+++ b/EDGAR_Form4_Insider_Purchases.xlsx
@@ -11,7 +11,8 @@
     <sheet name="Funnel" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Sample Data" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Verification" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Methodology" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Company KPIs" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +21,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="$#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="$#,##0"/>
     <numFmt numFmtId="167" formatCode="$#,##0,,&quot;M&quot;"/>
+    <numFmt numFmtId="168" formatCode="$#,##0;($#,##0)"/>
+    <numFmt numFmtId="169" formatCode="$#,##0.00;($#,##0.00)"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="32">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -184,6 +187,16 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="001A1A1A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00B5472F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="14"/>
     </font>
@@ -194,7 +207,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -214,6 +227,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E7EEF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8E4DF"/>
       </patternFill>
     </fill>
   </fills>
@@ -243,7 +261,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -323,8 +341,29 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -422,6 +461,29 @@
     <tableColumn id="16" name="$200M–$20B band?"/>
     <tableColumn id="17" name="SIC"/>
     <tableColumn id="18" name="Source filing (EDGAR)"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompanyKPIs" displayName="CompanyKPIs" ref="B1:O36" headerRowCount="1">
+  <autoFilter ref="B1:O36"/>
+  <tableColumns count="14">
+    <tableColumn id="2" name="Issuer"/>
+    <tableColumn id="3" name="Ticker"/>
+    <tableColumn id="4" name="Issuer CIK"/>
+    <tableColumn id="5" name="Revenue"/>
+    <tableColumn id="6" name="Net Income"/>
+    <tableColumn id="7" name="Total Assets"/>
+    <tableColumn id="8" name="Total Liabilities"/>
+    <tableColumn id="9" name="Stockholders' Equity"/>
+    <tableColumn id="10" name="EPS (diluted)"/>
+    <tableColumn id="11" name="Operating Cash Flow"/>
+    <tableColumn id="12" name="Shares Outstanding"/>
+    <tableColumn id="13" name="Balance sheet as of"/>
+    <tableColumn id="14" name="Latest 10-K/10-Q filed"/>
+    <tableColumn id="15" name="Status"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showRowStripes="1"/>
 </table>
@@ -716,7 +778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E33"/>
+  <dimension ref="B2:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -941,17 +1003,30 @@
     <row r="33">
       <c r="B33" s="14" t="inlineStr">
         <is>
+          <t>Company KPIs</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>Revenue, net income, assets, liabilities, equity, EPS, operating cash flow, and shares outstanding for all 35 unique issuers, pulled from SEC XBRL — most-recent-available-today basis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="14" t="inlineStr">
+        <is>
           <t>Methodology</t>
         </is>
       </c>
-      <c r="C33" s="15" t="inlineStr">
+      <c r="C34" s="15" t="inlineStr">
         <is>
           <t>Data sources, filter definitions, sampling seed, and every documented assumption.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
+    <mergeCell ref="C34:D34"/>
     <mergeCell ref="B26:D27"/>
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="C30:D30"/>
@@ -5364,7 +5439,2015 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C2:C35"/>
+  <dimension ref="A1:O42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="17" t="n"/>
+      <c r="B1" s="17" t="inlineStr">
+        <is>
+          <t>Issuer</t>
+        </is>
+      </c>
+      <c r="C1" s="17" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="D1" s="17" t="inlineStr">
+        <is>
+          <t>Issuer CIK</t>
+        </is>
+      </c>
+      <c r="E1" s="17" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="F1" s="17" t="inlineStr">
+        <is>
+          <t>Net Income</t>
+        </is>
+      </c>
+      <c r="G1" s="17" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="H1" s="17" t="inlineStr">
+        <is>
+          <t>Total Liabilities</t>
+        </is>
+      </c>
+      <c r="I1" s="17" t="inlineStr">
+        <is>
+          <t>Stockholders' Equity</t>
+        </is>
+      </c>
+      <c r="J1" s="17" t="inlineStr">
+        <is>
+          <t>EPS (diluted)</t>
+        </is>
+      </c>
+      <c r="K1" s="17" t="inlineStr">
+        <is>
+          <t>Operating Cash Flow</t>
+        </is>
+      </c>
+      <c r="L1" s="17" t="inlineStr">
+        <is>
+          <t>Shares Outstanding</t>
+        </is>
+      </c>
+      <c r="M1" s="17" t="inlineStr">
+        <is>
+          <t>Balance sheet as of</t>
+        </is>
+      </c>
+      <c r="N1" s="17" t="inlineStr">
+        <is>
+          <t>Latest 10-K/10-Q filed</t>
+        </is>
+      </c>
+      <c r="O1" s="17" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="43" t="inlineStr">
+        <is>
+          <t>AKAMAI TECHNOLOGIES INC</t>
+        </is>
+      </c>
+      <c r="C2" s="43" t="inlineStr">
+        <is>
+          <t>AKAM</t>
+        </is>
+      </c>
+      <c r="D2" s="43" t="n">
+        <v>1086222</v>
+      </c>
+      <c r="E2" s="44" t="n">
+        <v>4208175000</v>
+      </c>
+      <c r="F2" s="45" t="n">
+        <v>452031000</v>
+      </c>
+      <c r="G2" s="44" t="n">
+        <v>15073420000</v>
+      </c>
+      <c r="H2" s="44" t="n">
+        <v>10324903000</v>
+      </c>
+      <c r="I2" s="45" t="n">
+        <v>4748517000</v>
+      </c>
+      <c r="J2" s="46" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="K2" s="45" t="n">
+        <v>1518765000</v>
+      </c>
+      <c r="L2" s="47" t="n">
+        <v>143716609</v>
+      </c>
+      <c r="M2" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="N2" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="O2" s="48" t="inlineStr">
+        <is>
+          <t>Actively SEC-reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="43" t="inlineStr">
+        <is>
+          <t>ANDEAVOR LOGISTICS LP</t>
+        </is>
+      </c>
+      <c r="C3" s="43" t="inlineStr">
+        <is>
+          <t>ANDX</t>
+        </is>
+      </c>
+      <c r="D3" s="43" t="n">
+        <v>1507615</v>
+      </c>
+      <c r="E3" s="44" t="n">
+        <v>623000000</v>
+      </c>
+      <c r="F3" s="45" t="n">
+        <v>628000000</v>
+      </c>
+      <c r="G3" s="44" t="n">
+        <v>10550000000</v>
+      </c>
+      <c r="H3" s="44" t="n">
+        <v>6016000000</v>
+      </c>
+      <c r="I3" s="45" t="n">
+        <v>4534000000</v>
+      </c>
+      <c r="J3" s="46" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="K3" s="45" t="n">
+        <v>1029000000</v>
+      </c>
+      <c r="L3" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="43" t="inlineStr">
+        <is>
+          <t>2019-06-30</t>
+        </is>
+      </c>
+      <c r="N3" s="43" t="inlineStr">
+        <is>
+          <t>2019-08-05</t>
+        </is>
+      </c>
+      <c r="O3" s="49" t="inlineStr">
+        <is>
+          <t>Likely delisted/inactive since 2019-08-05 (last SEC financials on file)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="43" t="inlineStr">
+        <is>
+          <t>ARES CAPITAL CORP</t>
+        </is>
+      </c>
+      <c r="C4" s="43" t="inlineStr">
+        <is>
+          <t>ARCC</t>
+        </is>
+      </c>
+      <c r="D4" s="43" t="n">
+        <v>1287750</v>
+      </c>
+      <c r="E4" s="44" t="n">
+        <v>3052000000</v>
+      </c>
+      <c r="F4" s="45" t="n">
+        <v>1299000000</v>
+      </c>
+      <c r="G4" s="44" t="n">
+        <v>30679000000</v>
+      </c>
+      <c r="H4" s="44" t="n">
+        <v>16614000000</v>
+      </c>
+      <c r="I4" s="45" t="n">
+        <v>14065000000</v>
+      </c>
+      <c r="J4" s="46" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="K4" s="45" t="n">
+        <v>-1717000000</v>
+      </c>
+      <c r="L4" s="47" t="n">
+        <v>718022845</v>
+      </c>
+      <c r="M4" s="43" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="N4" s="43" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="O4" s="48" t="inlineStr">
+        <is>
+          <t>Actively SEC-reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="43" t="inlineStr">
+        <is>
+          <t>ASSURED GUARANTY LTD</t>
+        </is>
+      </c>
+      <c r="C5" s="43" t="inlineStr">
+        <is>
+          <t>AGO</t>
+        </is>
+      </c>
+      <c r="D5" s="43" t="n">
+        <v>1273813</v>
+      </c>
+      <c r="E5" s="44" t="n">
+        <v>1110000000</v>
+      </c>
+      <c r="F5" s="45" t="n">
+        <v>503000000</v>
+      </c>
+      <c r="G5" s="44" t="n">
+        <v>12641000000</v>
+      </c>
+      <c r="H5" s="44" t="n">
+        <v>7059000000</v>
+      </c>
+      <c r="I5" s="45" t="n">
+        <v>5559000000</v>
+      </c>
+      <c r="J5" s="46" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="K5" s="45" t="n">
+        <v>259000000</v>
+      </c>
+      <c r="L5" s="47" t="n">
+        <v>43979208</v>
+      </c>
+      <c r="M5" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="N5" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="O5" s="48" t="inlineStr">
+        <is>
+          <t>Actively SEC-reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="43" t="inlineStr">
+        <is>
+          <t>Aegerion Pharmaceuticals, Inc.</t>
+        </is>
+      </c>
+      <c r="C6" s="43" t="inlineStr">
+        <is>
+          <t>AEGR</t>
+        </is>
+      </c>
+      <c r="D6" s="43" t="n">
+        <v>1338042</v>
+      </c>
+      <c r="E6" s="44" t="n">
+        <v>49003000</v>
+      </c>
+      <c r="F6" s="45" t="n">
+        <v>-36599000</v>
+      </c>
+      <c r="G6" s="44" t="n">
+        <v>353826000</v>
+      </c>
+      <c r="H6" s="44" t="n">
+        <v>366652000</v>
+      </c>
+      <c r="I6" s="45" t="n">
+        <v>-12826000</v>
+      </c>
+      <c r="J6" s="46" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="K6" s="45" t="n">
+        <v>15981000</v>
+      </c>
+      <c r="L6" s="47" t="n">
+        <v>29545088</v>
+      </c>
+      <c r="M6" s="43" t="inlineStr">
+        <is>
+          <t>2016-09-30</t>
+        </is>
+      </c>
+      <c r="N6" s="43" t="inlineStr">
+        <is>
+          <t>2016-11-04</t>
+        </is>
+      </c>
+      <c r="O6" s="49" t="inlineStr">
+        <is>
+          <t>Likely delisted/inactive since 2016-11-04 (last SEC financials on file)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>American Assets Trust, Inc.</t>
+        </is>
+      </c>
+      <c r="C7" s="43" t="inlineStr">
+        <is>
+          <t>AAT</t>
+        </is>
+      </c>
+      <c r="D7" s="43" t="n">
+        <v>1500217</v>
+      </c>
+      <c r="E7" s="44" t="n">
+        <v>110086000</v>
+      </c>
+      <c r="F7" s="45" t="n">
+        <v>3148000</v>
+      </c>
+      <c r="G7" s="44" t="n">
+        <v>2900567000</v>
+      </c>
+      <c r="H7" s="44" t="n">
+        <v>1827850000</v>
+      </c>
+      <c r="I7" s="45" t="n">
+        <v>1136575000</v>
+      </c>
+      <c r="J7" s="46" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K7" s="45" t="n">
+        <v>167115000</v>
+      </c>
+      <c r="L7" s="47" t="n">
+        <v>61390936</v>
+      </c>
+      <c r="M7" s="43" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="N7" s="43" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="O7" s="48" t="inlineStr">
+        <is>
+          <t>Actively SEC-reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>Bunge LTD</t>
+        </is>
+      </c>
+      <c r="C8" s="43" t="inlineStr">
+        <is>
+          <t>BG</t>
+        </is>
+      </c>
+      <c r="D8" s="43" t="n">
+        <v>1144519</v>
+      </c>
+      <c r="E8" s="44" t="n">
+        <v>16660000000</v>
+      </c>
+      <c r="F8" s="45" t="n">
+        <v>336000000</v>
+      </c>
+      <c r="G8" s="44" t="n">
+        <v>25133000000</v>
+      </c>
+      <c r="H8" s="44" t="n">
+        <v>14882000000</v>
+      </c>
+      <c r="I8" s="45" t="n">
+        <v>10251000000</v>
+      </c>
+      <c r="J8" s="46" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="K8" s="45" t="n">
+        <v>-5549000000</v>
+      </c>
+      <c r="L8" s="47" t="n">
+        <v>145287978</v>
+      </c>
+      <c r="M8" s="43" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="N8" s="43" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="O8" s="49" t="inlineStr">
+        <is>
+          <t>Likely delisted/inactive since 2023-10-26 (last SEC financials on file)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="43" t="inlineStr">
+        <is>
+          <t>CEDAR FAIR L P</t>
+        </is>
+      </c>
+      <c r="C9" s="43" t="inlineStr">
+        <is>
+          <t>FUN</t>
+        </is>
+      </c>
+      <c r="D9" s="43" t="n">
+        <v>811532</v>
+      </c>
+      <c r="E9" s="44" t="n">
+        <v>1798668000</v>
+      </c>
+      <c r="F9" s="45" t="n">
+        <v>124559000</v>
+      </c>
+      <c r="G9" s="44" t="n">
+        <v>2264265000</v>
+      </c>
+      <c r="H9" s="44" t="n">
+        <v>2995184000</v>
+      </c>
+      <c r="I9" s="45" t="n">
+        <v>-730919000</v>
+      </c>
+      <c r="J9" s="46" t="n"/>
+      <c r="K9" s="45" t="n">
+        <v>325675000</v>
+      </c>
+      <c r="L9" s="47" t="n">
+        <v>51252360</v>
+      </c>
+      <c r="M9" s="43" t="inlineStr">
+        <is>
+          <t>2024-03-31</t>
+        </is>
+      </c>
+      <c r="N9" s="43" t="inlineStr">
+        <is>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="O9" s="49" t="inlineStr">
+        <is>
+          <t>Likely delisted/inactive since 2024-05-09 (last SEC financials on file)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="43" t="inlineStr">
+        <is>
+          <t>COMSCORE, INC.</t>
+        </is>
+      </c>
+      <c r="C10" s="43" t="inlineStr">
+        <is>
+          <t>SCOR</t>
+        </is>
+      </c>
+      <c r="D10" s="43" t="n">
+        <v>1158172</v>
+      </c>
+      <c r="E10" s="44" t="n">
+        <v>357469000</v>
+      </c>
+      <c r="F10" s="45" t="n">
+        <v>-10004000</v>
+      </c>
+      <c r="G10" s="44" t="n">
+        <v>327530000</v>
+      </c>
+      <c r="H10" s="44" t="n">
+        <v>148408000</v>
+      </c>
+      <c r="I10" s="45" t="n">
+        <v>89468000</v>
+      </c>
+      <c r="J10" s="46" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="K10" s="45" t="n">
+        <v>22736000</v>
+      </c>
+      <c r="L10" s="47" t="n">
+        <v>15184326</v>
+      </c>
+      <c r="M10" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="N10" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="O10" s="48" t="inlineStr">
+        <is>
+          <t>Actively SEC-reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="43" t="inlineStr">
+        <is>
+          <t>CULLEN/FROST BANKERS, INC.</t>
+        </is>
+      </c>
+      <c r="C11" s="43" t="inlineStr">
+        <is>
+          <t>CFR</t>
+        </is>
+      </c>
+      <c r="D11" s="43" t="n">
+        <v>39263</v>
+      </c>
+      <c r="E11" s="44" t="n">
+        <v>2235244000</v>
+      </c>
+      <c r="F11" s="45" t="n">
+        <v>648557000</v>
+      </c>
+      <c r="G11" s="44" t="n">
+        <v>53881091000</v>
+      </c>
+      <c r="H11" s="44" t="n">
+        <v>49258448000</v>
+      </c>
+      <c r="I11" s="45" t="n">
+        <v>4622643000</v>
+      </c>
+      <c r="J11" s="46" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="K11" s="45" t="n">
+        <v>273979000</v>
+      </c>
+      <c r="L11" s="47" t="n">
+        <v>62148785</v>
+      </c>
+      <c r="M11" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="N11" s="43" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="O11" s="48" t="inlineStr">
+        <is>
+          <t>Actively SEC-reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="43" t="inlineStr">
+        <is>
+          <t>Donnelley Financial Solutions, Inc.</t>
+        </is>
+      </c>
+      <c r="C12" s="43" t="inlineStr">
+        <is>
+          <t>DFIN</t>
+        </is>
+      </c>
+      <c r="D12" s="43" t="n">
+        <v>1669811</v>
+      </c>
+      <c r="E12" s="44" t="n">
+        <v>767000000</v>
+      </c>
+      <c r="F12" s="45" t="n">
+        <v>32400000</v>
+      </c>
+      <c r="G12" s="44" t="n">
+        <v>834300000</v>
+      </c>
+      <c r="H12" s="44" t="n">
+        <v>446900000</v>
+      </c>
+      <c r="I12" s="45" t="n">
+        <v>387400000</v>
+      </c>
+      <c r="J12" s="46" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="K12" s="45" t="n">
+        <v>164900000</v>
+      </c>
+      <c r="L12" s="47" t="n">
+        <v>24585383</v>
+      </c>
+      <c r="M12" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="N12" s="43" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="O12" s="48" t="inlineStr">
+        <is>
+          <t>Actively SEC-reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="43" t="inlineStr">
+        <is>
+          <t>Extended Stay America, Inc.</t>
+        </is>
+      </c>
+      <c r="C13" s="43" t="inlineStr">
+        <is>
+          <t>STAY</t>
+        </is>
+      </c>
+      <c r="D13" s="43" t="n">
+        <v>1581164</v>
+      </c>
+      <c r="E13" s="44" t="n">
+        <v>1042316000</v>
+      </c>
+      <c r="F13" s="45" t="n">
+        <v>96256000</v>
+      </c>
+      <c r="G13" s="44" t="n">
+        <v>4020348000</v>
+      </c>
+      <c r="H13" s="44" t="n">
+        <v>2885693000</v>
+      </c>
+      <c r="I13" s="45" t="n">
+        <v>1134655000</v>
+      </c>
+      <c r="J13" s="46" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K13" s="45" t="n">
+        <v>218751000</v>
+      </c>
+      <c r="L13" s="47" t="n">
+        <v>177730773</v>
+      </c>
+      <c r="M13" s="43" t="inlineStr">
+        <is>
+          <t>2021-03-31</t>
+        </is>
+      </c>
+      <c r="N13" s="43" t="inlineStr">
+        <is>
+          <t>2021-05-10</t>
+        </is>
+      </c>
+      <c r="O13" s="49" t="inlineStr">
+        <is>
+          <t>Likely delisted/inactive since 2021-05-10 (last SEC financials on file)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="43" t="inlineStr">
+        <is>
+          <t>Fortress Transportation &amp; Infrastructure Investors LLC</t>
+        </is>
+      </c>
+      <c r="C14" s="43" t="inlineStr">
+        <is>
+          <t>FTAI</t>
+        </is>
+      </c>
+      <c r="D14" s="43" t="n">
+        <v>1590364</v>
+      </c>
+      <c r="E14" s="44" t="n">
+        <v>2507409000</v>
+      </c>
+      <c r="F14" s="45" t="n">
+        <v>501064000</v>
+      </c>
+      <c r="G14" s="44" t="n">
+        <v>4489162000</v>
+      </c>
+      <c r="H14" s="44" t="n">
+        <v>4085175000</v>
+      </c>
+      <c r="I14" s="45" t="n">
+        <v>403987000</v>
+      </c>
+      <c r="J14" s="46" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K14" s="45" t="n">
+        <v>-310745000</v>
+      </c>
+      <c r="L14" s="47" t="n">
+        <v>102707091</v>
+      </c>
+      <c r="M14" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="N14" s="43" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="O14" s="48" t="inlineStr">
+        <is>
+          <t>Actively SEC-reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="43" t="inlineStr">
+        <is>
+          <t>Freshpet, Inc.</t>
+        </is>
+      </c>
+      <c r="C15" s="43" t="inlineStr">
+        <is>
+          <t>FRPT</t>
+        </is>
+      </c>
+      <c r="D15" s="43" t="n">
+        <v>1611647</v>
+      </c>
+      <c r="E15" s="44" t="n">
+        <v>1102015000</v>
+      </c>
+      <c r="F15" s="45" t="n">
+        <v>139137000</v>
+      </c>
+      <c r="G15" s="44" t="n">
+        <v>1812415000</v>
+      </c>
+      <c r="H15" s="44" t="n">
+        <v>574719000</v>
+      </c>
+      <c r="I15" s="45" t="n">
+        <v>1237696000</v>
+      </c>
+      <c r="J15" s="46" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K15" s="45" t="n">
+        <v>160561000</v>
+      </c>
+      <c r="L15" s="47" t="n">
+        <v>48058074</v>
+      </c>
+      <c r="M15" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="N15" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="O15" s="48" t="inlineStr">
+        <is>
+          <t>Actively SEC-reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="43" t="inlineStr">
+        <is>
+          <t>GEO GROUP INC</t>
+        </is>
+      </c>
+      <c r="C16" s="43" t="inlineStr">
+        <is>
+          <t>GEO</t>
+        </is>
+      </c>
+      <c r="D16" s="43" t="n">
+        <v>923796</v>
+      </c>
+      <c r="E16" s="44" t="n">
+        <v>2631549000</v>
+      </c>
+      <c r="F16" s="45" t="n">
+        <v>254372000</v>
+      </c>
+      <c r="G16" s="44" t="n">
+        <v>3742262000</v>
+      </c>
+      <c r="H16" s="44" t="n">
+        <v>2225827000</v>
+      </c>
+      <c r="I16" s="45" t="n">
+        <v>1516435000</v>
+      </c>
+      <c r="J16" s="46" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="K16" s="45" t="n">
+        <v>72611000</v>
+      </c>
+      <c r="L16" s="47" t="n">
+        <v>131619584</v>
+      </c>
+      <c r="M16" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="N16" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="O16" s="48" t="inlineStr">
+        <is>
+          <t>Actively SEC-reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="43" t="inlineStr">
+        <is>
+          <t>Globalstar, Inc.</t>
+        </is>
+      </c>
+      <c r="C17" s="43" t="inlineStr">
+        <is>
+          <t>GSAT</t>
+        </is>
+      </c>
+      <c r="D17" s="43" t="n">
+        <v>1366868</v>
+      </c>
+      <c r="E17" s="44" t="n">
+        <v>272986000</v>
+      </c>
+      <c r="F17" s="45" t="n">
+        <v>-8651000</v>
+      </c>
+      <c r="G17" s="44" t="n">
+        <v>2444812000</v>
+      </c>
+      <c r="H17" s="44" t="n">
+        <v>2152199000</v>
+      </c>
+      <c r="I17" s="45" t="n">
+        <v>292613000</v>
+      </c>
+      <c r="J17" s="46" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="K17" s="45" t="n">
+        <v>621650000</v>
+      </c>
+      <c r="L17" s="47" t="n">
+        <v>126442583</v>
+      </c>
+      <c r="M17" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="N17" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="O17" s="48" t="inlineStr">
+        <is>
+          <t>Actively SEC-reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="43" t="inlineStr">
+        <is>
+          <t>GrubHub Inc.</t>
+        </is>
+      </c>
+      <c r="C18" s="43" t="inlineStr">
+        <is>
+          <t>GRUB</t>
+        </is>
+      </c>
+      <c r="D18" s="43" t="n">
+        <v>1594109</v>
+      </c>
+      <c r="E18" s="44" t="n">
+        <v>1819982000</v>
+      </c>
+      <c r="F18" s="45" t="n">
+        <v>-155861000</v>
+      </c>
+      <c r="G18" s="44" t="n">
+        <v>2362471000</v>
+      </c>
+      <c r="H18" s="44" t="n">
+        <v>1003448000</v>
+      </c>
+      <c r="I18" s="45" t="n">
+        <v>1359023000</v>
+      </c>
+      <c r="J18" s="46" t="n">
+        <v>-1.69</v>
+      </c>
+      <c r="K18" s="45" t="n">
+        <v>134994000</v>
+      </c>
+      <c r="L18" s="47" t="n">
+        <v>93347973</v>
+      </c>
+      <c r="M18" s="43" t="inlineStr">
+        <is>
+          <t>2021-03-31</t>
+        </is>
+      </c>
+      <c r="N18" s="43" t="inlineStr">
+        <is>
+          <t>2021-05-06</t>
+        </is>
+      </c>
+      <c r="O18" s="49" t="inlineStr">
+        <is>
+          <t>Likely delisted/inactive since 2021-05-06 (last SEC financials on file)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="43" t="inlineStr">
+        <is>
+          <t>HORNBECK OFFSHORE SERVICES INC /LA</t>
+        </is>
+      </c>
+      <c r="C19" s="43" t="inlineStr">
+        <is>
+          <t>HOS</t>
+        </is>
+      </c>
+      <c r="D19" s="43" t="n">
+        <v>1131227</v>
+      </c>
+      <c r="E19" s="44" t="n">
+        <v>225662000</v>
+      </c>
+      <c r="F19" s="45" t="n">
+        <v>-138814000</v>
+      </c>
+      <c r="G19" s="44" t="n">
+        <v>2520259000</v>
+      </c>
+      <c r="H19" s="44" t="n">
+        <v>1420472000</v>
+      </c>
+      <c r="I19" s="45" t="n">
+        <v>1099787000</v>
+      </c>
+      <c r="J19" s="46" t="n">
+        <v>-3.66</v>
+      </c>
+      <c r="K19" s="45" t="n">
+        <v>-87986000</v>
+      </c>
+      <c r="L19" s="47" t="n">
+        <v>39638729</v>
+      </c>
+      <c r="M19" s="43" t="inlineStr">
+        <is>
+          <t>2020-03-31</t>
+        </is>
+      </c>
+      <c r="N19" s="43" t="inlineStr">
+        <is>
+          <t>2020-07-29</t>
+        </is>
+      </c>
+      <c r="O19" s="49" t="inlineStr">
+        <is>
+          <t>Likely delisted/inactive since 2020-07-29 (last SEC financials on file)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="43" t="inlineStr">
+        <is>
+          <t>Hillman Solutions Corp.</t>
+        </is>
+      </c>
+      <c r="C20" s="43" t="inlineStr">
+        <is>
+          <t>HLMN</t>
+        </is>
+      </c>
+      <c r="D20" s="43" t="n">
+        <v>1822492</v>
+      </c>
+      <c r="E20" s="44" t="n">
+        <v>1552224000</v>
+      </c>
+      <c r="F20" s="45" t="n">
+        <v>40305000</v>
+      </c>
+      <c r="G20" s="44" t="n">
+        <v>2376178000</v>
+      </c>
+      <c r="H20" s="44" t="n">
+        <v>1150971000</v>
+      </c>
+      <c r="I20" s="45" t="n">
+        <v>1225207000</v>
+      </c>
+      <c r="J20" s="46" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K20" s="45" t="n">
+        <v>105185000</v>
+      </c>
+      <c r="L20" s="47" t="n">
+        <v>194544999</v>
+      </c>
+      <c r="M20" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="N20" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="O20" s="48" t="inlineStr">
+        <is>
+          <t>Actively SEC-reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="43" t="inlineStr">
+        <is>
+          <t>INPHI Corp</t>
+        </is>
+      </c>
+      <c r="C21" s="43" t="inlineStr">
+        <is>
+          <t>IPHI</t>
+        </is>
+      </c>
+      <c r="D21" s="43" t="n">
+        <v>1160958</v>
+      </c>
+      <c r="E21" s="44" t="n">
+        <v>187541000</v>
+      </c>
+      <c r="F21" s="45" t="n">
+        <v>-12027000</v>
+      </c>
+      <c r="G21" s="44" t="n">
+        <v>1008236000</v>
+      </c>
+      <c r="H21" s="44" t="n">
+        <v>654526000</v>
+      </c>
+      <c r="I21" s="45" t="n">
+        <v>353710000</v>
+      </c>
+      <c r="J21" s="46" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="K21" s="45" t="n">
+        <v>155585000</v>
+      </c>
+      <c r="L21" s="47" t="n">
+        <v>53672718</v>
+      </c>
+      <c r="M21" s="43" t="inlineStr">
+        <is>
+          <t>2020-12-31</t>
+        </is>
+      </c>
+      <c r="N21" s="43" t="inlineStr">
+        <is>
+          <t>2021-02-25</t>
+        </is>
+      </c>
+      <c r="O21" s="49" t="inlineStr">
+        <is>
+          <t>Likely delisted/inactive since 2021-02-25 (last SEC financials on file)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="43" t="inlineStr">
+        <is>
+          <t>ION GEOPHYSICAL CORP</t>
+        </is>
+      </c>
+      <c r="C22" s="43" t="inlineStr">
+        <is>
+          <t>IO</t>
+        </is>
+      </c>
+      <c r="D22" s="43" t="n">
+        <v>866609</v>
+      </c>
+      <c r="E22" s="44" t="n">
+        <v>27295000</v>
+      </c>
+      <c r="F22" s="45" t="n">
+        <v>-13136000</v>
+      </c>
+      <c r="G22" s="44" t="n">
+        <v>190908000</v>
+      </c>
+      <c r="H22" s="44" t="n">
+        <v>256073000</v>
+      </c>
+      <c r="I22" s="45" t="n">
+        <v>-66384000</v>
+      </c>
+      <c r="J22" s="46" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="K22" s="45" t="n">
+        <v>9159000</v>
+      </c>
+      <c r="L22" s="47" t="n">
+        <v>29617040</v>
+      </c>
+      <c r="M22" s="43" t="inlineStr">
+        <is>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+      <c r="N22" s="43" t="inlineStr">
+        <is>
+          <t>2021-11-03</t>
+        </is>
+      </c>
+      <c r="O22" s="49" t="inlineStr">
+        <is>
+          <t>Likely delisted/inactive since 2021-11-03 (last SEC financials on file)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="43" t="inlineStr">
+        <is>
+          <t>James River Group Holdings, Ltd.</t>
+        </is>
+      </c>
+      <c r="C23" s="43" t="inlineStr">
+        <is>
+          <t>JRVR</t>
+        </is>
+      </c>
+      <c r="D23" s="43" t="n">
+        <v>1620459</v>
+      </c>
+      <c r="E23" s="44" t="n">
+        <v>687614000</v>
+      </c>
+      <c r="F23" s="45" t="n">
+        <v>47427000</v>
+      </c>
+      <c r="G23" s="44" t="n">
+        <v>4773078000</v>
+      </c>
+      <c r="H23" s="44" t="n">
+        <v>4117362000</v>
+      </c>
+      <c r="I23" s="45" t="n">
+        <v>522601000</v>
+      </c>
+      <c r="J23" s="46" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="K23" s="45" t="n">
+        <v>-18786000</v>
+      </c>
+      <c r="L23" s="47" t="n">
+        <v>46239030</v>
+      </c>
+      <c r="M23" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="N23" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="O23" s="48" t="inlineStr">
+        <is>
+          <t>Actively SEC-reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="43" t="inlineStr">
+        <is>
+          <t>MP Materials Corp. / DE</t>
+        </is>
+      </c>
+      <c r="C24" s="43" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="D24" s="43" t="n">
+        <v>1801368</v>
+      </c>
+      <c r="E24" s="44" t="n">
+        <v>224441000</v>
+      </c>
+      <c r="F24" s="45" t="n">
+        <v>-85874000</v>
+      </c>
+      <c r="G24" s="44" t="n">
+        <v>3726740000</v>
+      </c>
+      <c r="H24" s="44" t="n">
+        <v>1355793000</v>
+      </c>
+      <c r="I24" s="45" t="n">
+        <v>1957336000</v>
+      </c>
+      <c r="J24" s="46" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="K24" s="45" t="n">
+        <v>-155755000</v>
+      </c>
+      <c r="L24" s="47" t="n">
+        <v>178101588</v>
+      </c>
+      <c r="M24" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="N24" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="O24" s="48" t="inlineStr">
+        <is>
+          <t>Actively SEC-reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="43" t="inlineStr">
+        <is>
+          <t>NGM BIOPHARMACEUTICALS INC</t>
+        </is>
+      </c>
+      <c r="C25" s="43" t="inlineStr">
+        <is>
+          <t>NGM</t>
+        </is>
+      </c>
+      <c r="D25" s="43" t="n">
+        <v>1426332</v>
+      </c>
+      <c r="E25" s="44" t="n">
+        <v>4417000</v>
+      </c>
+      <c r="F25" s="45" t="n">
+        <v>-142375000</v>
+      </c>
+      <c r="G25" s="44" t="n">
+        <v>168868000</v>
+      </c>
+      <c r="H25" s="44" t="n">
+        <v>20230000</v>
+      </c>
+      <c r="I25" s="45" t="n">
+        <v>148638000</v>
+      </c>
+      <c r="J25" s="46" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="K25" s="45" t="n">
+        <v>-132202000</v>
+      </c>
+      <c r="L25" s="47" t="n">
+        <v>83462408</v>
+      </c>
+      <c r="M25" s="43" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="N25" s="43" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="O25" s="49" t="inlineStr">
+        <is>
+          <t>Likely delisted/inactive since 2024-03-11 (last SEC financials on file)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="43" t="inlineStr">
+        <is>
+          <t>NexPoint Real Estate Finance, Inc.</t>
+        </is>
+      </c>
+      <c r="C26" s="43" t="inlineStr">
+        <is>
+          <t>NREF</t>
+        </is>
+      </c>
+      <c r="D26" s="43" t="n">
+        <v>1786248</v>
+      </c>
+      <c r="E26" s="44" t="n">
+        <v>68358000</v>
+      </c>
+      <c r="F26" s="45" t="n">
+        <v>123143000</v>
+      </c>
+      <c r="G26" s="44" t="n">
+        <v>5367617000</v>
+      </c>
+      <c r="H26" s="44" t="n">
+        <v>4505249000</v>
+      </c>
+      <c r="I26" s="45" t="n">
+        <v>379706000</v>
+      </c>
+      <c r="J26" s="46" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="K26" s="45" t="n">
+        <v>22916000</v>
+      </c>
+      <c r="L26" s="47" t="n">
+        <v>18848029</v>
+      </c>
+      <c r="M26" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="N26" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="O26" s="48" t="inlineStr">
+        <is>
+          <t>Actively SEC-reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="43" t="inlineStr">
+        <is>
+          <t>OneMain Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="C27" s="43" t="inlineStr">
+        <is>
+          <t>OMF</t>
+        </is>
+      </c>
+      <c r="D27" s="43" t="n">
+        <v>1584207</v>
+      </c>
+      <c r="E27" s="44" t="n">
+        <v>5455000000</v>
+      </c>
+      <c r="F27" s="45" t="n">
+        <v>783000000</v>
+      </c>
+      <c r="G27" s="44" t="n">
+        <v>27018000000</v>
+      </c>
+      <c r="H27" s="44" t="n">
+        <v>23641000000</v>
+      </c>
+      <c r="I27" s="45" t="n">
+        <v>3377000000</v>
+      </c>
+      <c r="J27" s="46" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="K27" s="45" t="n">
+        <v>3132000000</v>
+      </c>
+      <c r="L27" s="47" t="n">
+        <v>115530952</v>
+      </c>
+      <c r="M27" s="43" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="N27" s="43" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="O27" s="48" t="inlineStr">
+        <is>
+          <t>Actively SEC-reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="43" t="inlineStr">
+        <is>
+          <t>PENN NATIONAL GAMING INC</t>
+        </is>
+      </c>
+      <c r="C28" s="43" t="inlineStr">
+        <is>
+          <t>PENN</t>
+        </is>
+      </c>
+      <c r="D28" s="43" t="n">
+        <v>921738</v>
+      </c>
+      <c r="E28" s="44" t="n">
+        <v>6961000000</v>
+      </c>
+      <c r="F28" s="45" t="n">
+        <v>-843100000</v>
+      </c>
+      <c r="G28" s="44" t="n">
+        <v>14069200000</v>
+      </c>
+      <c r="H28" s="44" t="n">
+        <v>12215400000</v>
+      </c>
+      <c r="I28" s="45" t="n">
+        <v>1861300000</v>
+      </c>
+      <c r="J28" s="46" t="n">
+        <v>-5.83</v>
+      </c>
+      <c r="K28" s="45" t="n">
+        <v>508200000</v>
+      </c>
+      <c r="L28" s="47" t="n">
+        <v>134066591</v>
+      </c>
+      <c r="M28" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="N28" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="O28" s="48" t="inlineStr">
+        <is>
+          <t>Actively SEC-reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="43" t="inlineStr">
+        <is>
+          <t>PENSKE AUTOMOTIVE GROUP, INC.</t>
+        </is>
+      </c>
+      <c r="C29" s="43" t="inlineStr">
+        <is>
+          <t>PAG</t>
+        </is>
+      </c>
+      <c r="D29" s="43" t="n">
+        <v>1019849</v>
+      </c>
+      <c r="E29" s="44" t="n">
+        <v>7769200000</v>
+      </c>
+      <c r="F29" s="45" t="n">
+        <v>186100000</v>
+      </c>
+      <c r="G29" s="44" t="n">
+        <v>18485300000</v>
+      </c>
+      <c r="H29" s="44" t="n">
+        <v>12651900000</v>
+      </c>
+      <c r="I29" s="45" t="n">
+        <v>5815300000</v>
+      </c>
+      <c r="J29" s="46" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="K29" s="45" t="n">
+        <v>975100000</v>
+      </c>
+      <c r="L29" s="47" t="n">
+        <v>65662873</v>
+      </c>
+      <c r="M29" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="N29" s="43" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="O29" s="48" t="inlineStr">
+        <is>
+          <t>Actively SEC-reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="43" t="inlineStr">
+        <is>
+          <t>REGIS CORP</t>
+        </is>
+      </c>
+      <c r="C30" s="43" t="inlineStr">
+        <is>
+          <t>RGS</t>
+        </is>
+      </c>
+      <c r="D30" s="43" t="n">
+        <v>716643</v>
+      </c>
+      <c r="E30" s="44" t="n">
+        <v>210134000</v>
+      </c>
+      <c r="F30" s="45" t="n">
+        <v>123536000</v>
+      </c>
+      <c r="G30" s="44" t="n">
+        <v>556598000</v>
+      </c>
+      <c r="H30" s="44" t="n">
+        <v>367148000</v>
+      </c>
+      <c r="I30" s="45" t="n">
+        <v>189450000</v>
+      </c>
+      <c r="J30" s="46" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="K30" s="45" t="n">
+        <v>13744000</v>
+      </c>
+      <c r="L30" s="47" t="n">
+        <v>2498778</v>
+      </c>
+      <c r="M30" s="43" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="N30" s="43" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="O30" s="48" t="inlineStr">
+        <is>
+          <t>Actively SEC-reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="43" t="inlineStr">
+        <is>
+          <t>Ryman Hospitality Properties, Inc.</t>
+        </is>
+      </c>
+      <c r="C31" s="43" t="inlineStr">
+        <is>
+          <t>RHP</t>
+        </is>
+      </c>
+      <c r="D31" s="43" t="n">
+        <v>1040829</v>
+      </c>
+      <c r="E31" s="44" t="n">
+        <v>2577061000</v>
+      </c>
+      <c r="F31" s="45" t="n">
+        <v>243425000</v>
+      </c>
+      <c r="G31" s="44" t="n">
+        <v>6191836000</v>
+      </c>
+      <c r="H31" s="44" t="n">
+        <v>4956640000</v>
+      </c>
+      <c r="I31" s="45" t="n">
+        <v>748321000</v>
+      </c>
+      <c r="J31" s="46" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="K31" s="45" t="n">
+        <v>590629000</v>
+      </c>
+      <c r="L31" s="47" t="n">
+        <v>63119288</v>
+      </c>
+      <c r="M31" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="N31" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="O31" s="48" t="inlineStr">
+        <is>
+          <t>Actively SEC-reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="43" t="inlineStr">
+        <is>
+          <t>SEARS HOLDINGS CORP</t>
+        </is>
+      </c>
+      <c r="C32" s="43" t="inlineStr">
+        <is>
+          <t>SHLD</t>
+        </is>
+      </c>
+      <c r="D32" s="43" t="n">
+        <v>1310067</v>
+      </c>
+      <c r="E32" s="44" t="n">
+        <v>2742000000</v>
+      </c>
+      <c r="F32" s="45" t="n">
+        <v>182000000</v>
+      </c>
+      <c r="G32" s="44" t="n">
+        <v>6677000000</v>
+      </c>
+      <c r="H32" s="44" t="n">
+        <v>7393000000</v>
+      </c>
+      <c r="I32" s="45" t="n">
+        <v>-5311000000</v>
+      </c>
+      <c r="J32" s="46" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="K32" s="45" t="n">
+        <v>-1842000000</v>
+      </c>
+      <c r="L32" s="47" t="n">
+        <v>109236080</v>
+      </c>
+      <c r="M32" s="43" t="inlineStr">
+        <is>
+          <t>2018-11-03</t>
+        </is>
+      </c>
+      <c r="N32" s="43" t="inlineStr">
+        <is>
+          <t>2018-12-13</t>
+        </is>
+      </c>
+      <c r="O32" s="49" t="inlineStr">
+        <is>
+          <t>Likely delisted/inactive since 2018-12-13 (last SEC financials on file)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="43" t="inlineStr">
+        <is>
+          <t>SM Energy Co</t>
+        </is>
+      </c>
+      <c r="C33" s="43" t="inlineStr">
+        <is>
+          <t>SM</t>
+        </is>
+      </c>
+      <c r="D33" s="43" t="n">
+        <v>893538</v>
+      </c>
+      <c r="E33" s="44" t="n">
+        <v>3154000000</v>
+      </c>
+      <c r="F33" s="45" t="n">
+        <v>648000000</v>
+      </c>
+      <c r="G33" s="44" t="n">
+        <v>18858000000</v>
+      </c>
+      <c r="H33" s="44" t="n">
+        <v>11045000000</v>
+      </c>
+      <c r="I33" s="45" t="n">
+        <v>7813000000</v>
+      </c>
+      <c r="J33" s="46" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="K33" s="45" t="n">
+        <v>2011000000</v>
+      </c>
+      <c r="L33" s="47" t="n">
+        <v>237854068</v>
+      </c>
+      <c r="M33" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="N33" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="O33" s="48" t="inlineStr">
+        <is>
+          <t>Actively SEC-reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="43" t="inlineStr">
+        <is>
+          <t>SUNPOWER CORP</t>
+        </is>
+      </c>
+      <c r="C34" s="43" t="inlineStr">
+        <is>
+          <t>SPWR</t>
+        </is>
+      </c>
+      <c r="D34" s="43" t="n">
+        <v>867773</v>
+      </c>
+      <c r="E34" s="44" t="n">
+        <v>497968000</v>
+      </c>
+      <c r="F34" s="45" t="n">
+        <v>3425000</v>
+      </c>
+      <c r="G34" s="44" t="n">
+        <v>1447332000</v>
+      </c>
+      <c r="H34" s="44" t="n">
+        <v>1023792000</v>
+      </c>
+      <c r="I34" s="45" t="n">
+        <v>422613000</v>
+      </c>
+      <c r="J34" s="46" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K34" s="45" t="n">
+        <v>-180897000</v>
+      </c>
+      <c r="L34" s="47" t="n">
+        <v>175361088</v>
+      </c>
+      <c r="M34" s="43" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="N34" s="43" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="O34" s="49" t="inlineStr">
+        <is>
+          <t>Likely delisted/inactive since 2023-12-18 (last SEC financials on file)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="43" t="inlineStr">
+        <is>
+          <t>Sarepta Therapeutics, Inc.</t>
+        </is>
+      </c>
+      <c r="C35" s="43" t="inlineStr">
+        <is>
+          <t>SRPT</t>
+        </is>
+      </c>
+      <c r="D35" s="43" t="n">
+        <v>873303</v>
+      </c>
+      <c r="E35" s="44" t="n">
+        <v>442934000</v>
+      </c>
+      <c r="F35" s="45" t="n">
+        <v>-412226000</v>
+      </c>
+      <c r="G35" s="44" t="n">
+        <v>3188512000</v>
+      </c>
+      <c r="H35" s="44" t="n">
+        <v>1660714000</v>
+      </c>
+      <c r="I35" s="45" t="n">
+        <v>1527798000</v>
+      </c>
+      <c r="J35" s="46" t="n">
+        <v>-3.93</v>
+      </c>
+      <c r="K35" s="45" t="n">
+        <v>-205479000</v>
+      </c>
+      <c r="L35" s="47" t="n">
+        <v>105627021</v>
+      </c>
+      <c r="M35" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="N35" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="O35" s="48" t="inlineStr">
+        <is>
+          <t>Actively SEC-reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="43" t="inlineStr">
+        <is>
+          <t>WhiteHorse Finance, Inc.</t>
+        </is>
+      </c>
+      <c r="C36" s="43" t="inlineStr">
+        <is>
+          <t>WHF</t>
+        </is>
+      </c>
+      <c r="D36" s="43" t="n">
+        <v>1552198</v>
+      </c>
+      <c r="E36" s="44" t="n">
+        <v>72672000</v>
+      </c>
+      <c r="F36" s="45" t="n">
+        <v>14337000</v>
+      </c>
+      <c r="G36" s="44" t="n">
+        <v>604082000</v>
+      </c>
+      <c r="H36" s="44" t="n">
+        <v>351270000</v>
+      </c>
+      <c r="I36" s="45" t="n">
+        <v>252812000</v>
+      </c>
+      <c r="J36" s="46" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="K36" s="45" t="n">
+        <v>77272000</v>
+      </c>
+      <c r="L36" s="47" t="n">
+        <v>21476471</v>
+      </c>
+      <c r="M36" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="N36" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="O36" s="48" t="inlineStr">
+        <is>
+          <t>Actively SEC-reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="35" t="inlineStr">
+        <is>
+          <t>Source: SEC XBRL company facts API (data.sec.gov/api/xbrl/companyfacts), most-recent-available-today basis (NOT point-in-time matched to any insider's filing date -- these are current/latest figures as currently on file with SEC). Revenue/Net Income/EPS/Operating Cash Flow use the latest full-year (10-K, fiscal-year) figure where available. Total Assets/Liabilities/Equity/Shares Outstanding use the latest balance-sheet date on file, which may be a 10-Q. Different filers tag economically-equivalent line items under different standard XBRL tags (e.g. BDCs report "GrossInvestmentIncomeOperating" instead of "Revenues"; LPs report "PartnersCapital" instead of "StockholdersEquity") -- the pull script tries multiple fallback tags per concept and always takes the single most-recent value found across all of them. Total Liabilities is derived (Total Assets − Stockholders' Equity) for filers that don't separately tag it. "Status" flags issuers whose most recent SEC financials predate 2025 -- for most of these that's because the company was acquired, went private, or went bankrupt after its Form 4 filing date (confirmed for several: Sears Holdings [2018 bankruptcy], Andeavor Logistics [2019 merger into MPLX], Hornbeck Offshore [2020 Chapter 11], Inphi [2021 acquired by Marvell], GrubHub [2021 acquired by Just Eat Takeaway], Extended Stay America [2021 taken private], Ion Geophysical [2022 bankruptcy], SunPower [2024 bankruptcy]) -- their KPIs are their last available figures, not stale data collection. One gap: Cedar Fair L.P. does not tag EPS under any standard XBRL concept found (it may report per-unit income only in narrative text, not tagged data) -- left blank rather than guessed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B38:I42"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="C2:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="2" max="2"/>
@@ -5372,14 +7455,14 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="C2" s="43" t="inlineStr">
+      <c r="C2" s="50" t="inlineStr">
         <is>
           <t>Methodology &amp; data sources</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="C4" s="44" t="inlineStr">
+      <c r="C4" s="51" t="inlineStr">
         <is>
           <t>Window</t>
         </is>
@@ -5393,7 +7476,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="C7" s="44" t="inlineStr">
+      <c r="C7" s="51" t="inlineStr">
         <is>
           <t>Filing discovery</t>
         </is>
@@ -5407,7 +7490,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="C10" s="44" t="inlineStr">
+      <c r="C10" s="51" t="inlineStr">
         <is>
           <t>Transaction data</t>
         </is>
@@ -5421,7 +7504,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="C13" s="44" t="inlineStr">
+      <c r="C13" s="51" t="inlineStr">
         <is>
           <t>Market cap</t>
         </is>
@@ -5435,7 +7518,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="C16" s="44" t="inlineStr">
+      <c r="C16" s="51" t="inlineStr">
         <is>
           <t>Exchange</t>
         </is>
@@ -5449,7 +7532,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="C19" s="44" t="inlineStr">
+      <c r="C19" s="51" t="inlineStr">
         <is>
           <t>Opportunistic screen</t>
         </is>
@@ -5463,7 +7546,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="C22" s="44" t="inlineStr">
+      <c r="C22" s="51" t="inlineStr">
         <is>
           <t>Rule 10b5-1 detection</t>
         </is>
@@ -5477,7 +7560,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="C25" s="44" t="inlineStr">
+      <c r="C25" s="51" t="inlineStr">
         <is>
           <t>Sampling design (seed = 42)</t>
         </is>
@@ -5491,7 +7574,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="C28" s="44" t="inlineStr">
+      <c r="C28" s="51" t="inlineStr">
         <is>
           <t>Duplicate rows found &amp; fixed</t>
         </is>
@@ -5505,7 +7588,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="C31" s="44" t="inlineStr">
+      <c r="C31" s="51" t="inlineStr">
         <is>
           <t>Verification</t>
         </is>
@@ -5519,7 +7602,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="C34" s="44" t="inlineStr">
+      <c r="C34" s="51" t="inlineStr">
         <is>
           <t>Not automated (by design)</t>
         </is>
@@ -5529,6 +7612,20 @@
       <c r="C35" s="13" t="inlineStr">
         <is>
           <t>"Was this person a proven founder/operator" was NOT attempted here — that is an explicitly manual, later research step per the task brief, not something to automate or guess at.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" s="51" t="inlineStr">
+        <is>
+          <t>Company KPIs sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="56" customHeight="1">
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>Revenue, Net Income, Total Assets, Total Liabilities, Stockholders' Equity, EPS (diluted), Operating Cash Flow, and Shares Outstanding for all 35 unique issuers in the sample, pulled from SEC's XBRL company facts API on a most-recent-available-today basis (per the user's explicit choice -- not point-in-time matched to each insider's filing date). Full source/tag/gap documentation is on that sheet's own footnote.</t>
         </is>
       </c>
     </row>
